--- a/Assets/Data/Dungeon0054.xlsx
+++ b/Assets/Data/Dungeon0054.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -52,22 +52,19 @@
     <t>■</t>
   </si>
   <si>
-    <t>Mv</t>
+    <t>Ar:D4</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Ar:D1</t>
   </si>
   <si>
     <t>Mg</t>
   </si>
   <si>
-    <t>Ar:D1</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Dr</t>
-  </si>
-  <si>
-    <t>Ar:D3</t>
+    <t>Mv</t>
   </si>
   <si>
     <t>Ar:D2</t>
@@ -108,9 +105,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -130,14 +127,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -152,38 +157,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -204,17 +178,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -223,6 +189,13 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -237,12 +210,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -272,6 +262,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -282,13 +279,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,7 +423,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -312,55 +441,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -372,97 +453,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -473,45 +470,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -533,8 +491,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -544,6 +502,45 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -581,19 +578,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -602,124 +605,118 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -742,12 +739,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -843,169 +840,185 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2010</v>
+            <v>1030</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョンから出る</v>
+            <v>メインイベント再生</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="E6" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2021</v>
+            <v>2011</v>
           </cell>
           <cell r="E7" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョンから出る（確認無し）</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>2030</v>
+            <v>2020</v>
           </cell>
           <cell r="E8" t="str">
-            <v>ダンジョンクリア</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3010</v>
+            <v>2021</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アーティファクト取得</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3020</v>
+            <v>2030</v>
           </cell>
           <cell r="E10" t="str">
-            <v>アイテム取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>3030</v>
+            <v>3010</v>
           </cell>
           <cell r="E11" t="str">
-            <v>魔法入手</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4010</v>
+            <v>3020</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を増やす</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4011</v>
+            <v>3030</v>
           </cell>
           <cell r="E13" t="str">
-            <v>仲間を外す</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>4020</v>
+            <v>4010</v>
           </cell>
           <cell r="E14" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5010</v>
+            <v>4011</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制戦闘</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>5020</v>
+            <v>4020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>強制ボス戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6010</v>
+            <v>5010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6011</v>
+            <v>5020</v>
           </cell>
           <cell r="E18" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6020</v>
+            <v>6010</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>6030</v>
+            <v>6011</v>
           </cell>
           <cell r="E20" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7010</v>
+            <v>6020</v>
           </cell>
           <cell r="E21" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7020</v>
+            <v>6030</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>7021</v>
+            <v>7010</v>
           </cell>
           <cell r="E23" t="str">
-            <v>怨嗟床解除</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
-            <v>8010</v>
+            <v>7020</v>
           </cell>
           <cell r="E24" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="25">
           <cell r="D25">
+            <v>7021</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>怨嗟床解除</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
+            <v>8010</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
             <v>9010</v>
           </cell>
-          <cell r="E25" t="str">
+          <cell r="E27" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
@@ -1342,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>14</v>
@@ -1501,15 +1514,9 @@
       <c r="O2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -1580,15 +1587,9 @@
       <c r="O3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
@@ -1659,15 +1660,9 @@
       <c r="O4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -1738,15 +1733,9 @@
       <c r="O5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -1788,22 +1777,22 @@
         <v>8</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>8</v>
@@ -1817,15 +1806,9 @@
       <c r="O6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -1864,13 +1847,13 @@
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>9</v>
@@ -1879,13 +1862,13 @@
         <v>9</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>8</v>
@@ -1896,15 +1879,9 @@
       <c r="O7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -1940,34 +1917,34 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>8</v>
@@ -1975,15 +1952,9 @@
       <c r="O8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -2019,19 +1990,19 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>13</v>
@@ -2040,13 +2011,13 @@
         <v>14</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>8</v>
@@ -2054,15 +2025,9 @@
       <c r="O9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -2098,34 +2063,34 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>8</v>
@@ -2133,15 +2098,9 @@
       <c r="O10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -2180,13 +2139,13 @@
         <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>9</v>
@@ -2195,13 +2154,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>8</v>
@@ -2212,15 +2171,9 @@
       <c r="O11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
@@ -2262,22 +2215,22 @@
         <v>8</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>8</v>
@@ -2291,15 +2244,9 @@
       <c r="O12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
@@ -2370,15 +2317,9 @@
       <c r="O13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
@@ -2449,15 +2390,9 @@
       <c r="O14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
@@ -2528,15 +2463,9 @@
       <c r="O15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
@@ -4051,22 +3980,22 @@
         <v>8</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>8</v>
@@ -4127,13 +4056,13 @@
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>9</v>
@@ -4142,13 +4071,13 @@
         <v>9</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>8</v>
@@ -4203,16 +4132,16 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>9</v>
@@ -4220,15 +4149,17 @@
       <c r="I8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="2"/>
+      <c r="J8" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>8</v>
@@ -4280,34 +4211,34 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="L9" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>8</v>
@@ -4359,34 +4290,34 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>8</v>
@@ -4441,13 +4372,13 @@
         <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>9</v>
@@ -4456,13 +4387,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>8</v>
@@ -4523,22 +4454,22 @@
         <v>8</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>8</v>
@@ -5890,7 +5821,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="7" max="7" width="24.4545454545455" customWidth="1"/>
@@ -5901,34 +5832,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>25</v>
-      </c>
-      <c r="K1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -5939,7 +5870,7 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>3010</v>
@@ -5958,7 +5889,7 @@
         <v>8</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -5969,7 +5900,7 @@
         <v>54</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -6002,10 +5933,10 @@
         <v>54</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>3010</v>
@@ -6035,10 +5966,10 @@
         <v>54</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>3010</v>
@@ -6068,23 +5999,23 @@
         <v>54</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>8010</v>
+        <v>1010</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F6,[1]Define!D:D))</f>
-        <v>指定リージョンを開示する</v>
+        <v>Adv再生</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6101,26 +6032,26 @@
         <v>54</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>3010</v>
       </c>
       <c r="F7">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="G7" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F7,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>エンフェリアイベント再生</v>
       </c>
       <c r="H7">
-        <v>140</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -6134,23 +6065,23 @@
         <v>54</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>3010</v>
       </c>
       <c r="F8">
-        <v>6010</v>
+        <v>9010</v>
       </c>
       <c r="G8" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F8,[1]Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H8">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6167,7 +6098,7 @@
         <v>54</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -6176,10 +6107,14 @@
         <v>3010</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>8010</v>
+      </c>
+      <c r="G9" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F9,[1]Define!D:D))</f>
+        <v>指定リージョンを開示する</v>
       </c>
       <c r="H9">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6188,72 +6123,6 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>54</v>
-      </c>
-      <c r="B10">
-        <v>8</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-      <c r="D10">
-        <v>3010</v>
-      </c>
-      <c r="F10">
-        <v>1020</v>
-      </c>
-      <c r="G10" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F10,[1]Define!D:D))</f>
-        <v>エンフェリアイベント再生</v>
-      </c>
-      <c r="H10">
-        <v>4</v>
-      </c>
-      <c r="I10">
-        <v>3</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>54</v>
-      </c>
-      <c r="B11">
-        <v>8</v>
-      </c>
-      <c r="C11">
-        <v>6</v>
-      </c>
-      <c r="D11">
-        <v>3010</v>
-      </c>
-      <c r="F11">
-        <v>9010</v>
-      </c>
-      <c r="G11" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F11,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/Dungeon0054.xlsx
+++ b/Assets/Data/Dungeon0054.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -126,8 +126,84 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -148,16 +224,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -172,45 +241,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,25 +255,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,20 +265,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,7 +279,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,7 +297,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,49 +351,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -363,7 +417,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -375,25 +429,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,49 +441,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -474,6 +474,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -491,41 +515,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -545,17 +551,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -578,7 +578,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -587,136 +587,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon0054.xlsx
+++ b/Assets/Data/Dungeon0054.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="24">
   <si>
     <t>Id</t>
   </si>
@@ -52,25 +52,19 @@
     <t>■</t>
   </si>
   <si>
-    <t>Ar:D4</t>
+    <t>Mv</t>
   </si>
   <si>
-    <t>No</t>
+    <t>Un</t>
   </si>
   <si>
-    <t>Ar:D1</t>
+    <t>Tr:D1</t>
   </si>
   <si>
     <t>Mg</t>
   </si>
   <si>
-    <t>Mv</t>
-  </si>
-  <si>
-    <t>Ar:D2</t>
-  </si>
-  <si>
-    <t>①</t>
+    <t>No</t>
   </si>
   <si>
     <t>PositionX</t>
@@ -105,9 +99,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -126,16 +120,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -143,25 +130,24 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -173,7 +159,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -194,6 +180,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -202,8 +196,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -211,22 +206,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,15 +221,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,10 +235,32 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -279,7 +273,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,7 +327,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,25 +345,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -333,19 +405,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -357,103 +447,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -473,25 +467,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -508,6 +489,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -555,18 +551,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -578,145 +572,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -796,9 +790,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Stages"/>
-      <sheetName val="StageEvents"/>
       <sheetName val="StageEnemyRates"/>
-      <sheetName val="Tutorials"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
     </sheetNames>
@@ -806,9 +798,7 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="D1" t="str">
             <v>Type</v>
@@ -1777,13 +1767,13 @@
         <v>8</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>8</v>
@@ -1847,19 +1837,19 @@
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>8</v>
@@ -1917,19 +1907,19 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>9</v>
@@ -1941,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>8</v>
@@ -1990,31 +1980,29 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>8</v>
@@ -2063,19 +2051,19 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>9</v>
@@ -2083,17 +2071,15 @@
       <c r="J10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>8</v>
@@ -2141,32 +2127,20 @@
       <c r="E11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
       <c r="M11" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>8</v>
@@ -2212,11 +2186,9 @@
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
         <v>9</v>
       </c>
@@ -2224,22 +2196,22 @@
         <v>9</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>8</v>
@@ -2285,28 +2257,28 @@
         <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>8</v>
@@ -2358,28 +2330,20 @@
         <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>8</v>
@@ -2431,28 +2395,28 @@
         <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>8</v>
@@ -3693,15 +3657,9 @@
       <c r="O2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -3772,15 +3730,9 @@
       <c r="O3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
@@ -3851,15 +3803,9 @@
       <c r="O4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -3930,15 +3876,9 @@
       <c r="O5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -3980,13 +3920,13 @@
         <v>8</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>8</v>
@@ -4009,15 +3949,9 @@
       <c r="O6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -4056,19 +3990,19 @@
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>8</v>
@@ -4088,15 +4022,9 @@
       <c r="O7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -4132,19 +4060,19 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>9</v>
@@ -4156,7 +4084,7 @@
         <v>9</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>8</v>
@@ -4167,15 +4095,9 @@
       <c r="O8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -4211,31 +4133,29 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>8</v>
@@ -4246,15 +4166,9 @@
       <c r="O9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -4290,19 +4204,19 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>9</v>
@@ -4310,30 +4224,22 @@
       <c r="J10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -4374,45 +4280,27 @@
       <c r="E11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
       <c r="M11" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
@@ -4451,11 +4339,9 @@
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
         <v>9</v>
       </c>
@@ -4463,35 +4349,29 @@
         <v>9</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
@@ -4530,28 +4410,28 @@
         <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>8</v>
@@ -4562,15 +4442,9 @@
       <c r="O13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
@@ -4609,28 +4483,20 @@
         <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>8</v>
@@ -4641,15 +4507,9 @@
       <c r="O14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
@@ -4688,28 +4548,28 @@
         <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>8</v>
@@ -4720,15 +4580,9 @@
       <c r="O15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
@@ -5832,34 +5686,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>23</v>
-      </c>
-      <c r="J1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -5867,10 +5721,10 @@
         <v>54</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>3010</v>
@@ -5886,10 +5740,10 @@
         <v>53</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -5900,7 +5754,7 @@
         <v>54</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -5909,23 +5763,23 @@
         <v>3010</v>
       </c>
       <c r="F3">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="G3" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F3,[1]Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H3">
-        <v>2060</v>
+        <v>55</v>
       </c>
       <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3" t="b">
         <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -5933,23 +5787,23 @@
         <v>54</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>3010</v>
       </c>
       <c r="F4">
-        <v>3010</v>
+        <v>3020</v>
       </c>
       <c r="G4" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F4,[1]Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H4">
-        <v>2070</v>
+        <v>3020</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5966,7 +5820,7 @@
         <v>54</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -5975,14 +5829,14 @@
         <v>3010</v>
       </c>
       <c r="F5">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="G5" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F5,[1]Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>ダンジョンクリア</v>
       </c>
       <c r="H5">
-        <v>2080</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6002,20 +5856,20 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>1010</v>
+        <v>5020</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F6,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H6">
-        <v>140</v>
+        <v>4010</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6032,26 +5886,26 @@
         <v>54</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>3010</v>
       </c>
       <c r="F7">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="G7" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F7,[1]Define!D:D))</f>
-        <v>エンフェリアイベント再生</v>
+        <v>Adv再生</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -6065,26 +5919,26 @@
         <v>54</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D8">
         <v>3010</v>
       </c>
       <c r="F8">
-        <v>9010</v>
+        <v>1020</v>
       </c>
       <c r="G8" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F8,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>エンフェリアイベント再生</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -6098,23 +5952,23 @@
         <v>54</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>3010</v>
       </c>
       <c r="F9">
-        <v>8010</v>
+        <v>9010</v>
       </c>
       <c r="G9" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F9,[1]Define!D:D))</f>
-        <v>指定リージョンを開示する</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
